--- a/app/reports/SGST_research.xlsx
+++ b/app/reports/SGST_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-11 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04527999877929687</v>
+        <v>0.04479000091552734</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/SGST_research.xlsx
+++ b/app/reports/SGST_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-12 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-13 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04479000091552734</v>
+        <v>0.04486999988555909</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/SGST_research.xlsx
+++ b/app/reports/SGST_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-13 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/SGST_research.xlsx
+++ b/app/reports/SGST_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-14 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04486999988555909</v>
+        <v>0.04468999862670898</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/SGST_research.xlsx
+++ b/app/reports/SGST_research.xlsx
@@ -614,7 +614,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-15 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-16 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.04468999862670898</v>
+        <v>0.04425999641418457</v>
       </c>
     </row>
     <row r="6">
